--- a/investor_forms/004_investment_performance_disclosure_consent_form--investor_forms.xlsx
+++ b/investor_forms/004_investment_performance_disclosure_consent_form--investor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,41 +520,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_1</t>
+          <t>consent</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>investment_performance_disclosure_consent_form</t>
+          <t>Is the investment performance disclosure consent form necessary for you, as an investor?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>investor_forms</t>
+          <t>What is your name?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,41 +566,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>What is your email address?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>investment_date</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>the_investment_performance_disclosure_consent_form</t>
+          <t>When was your investment made?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>investment_type</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>investor_forms</t>
+          <t>What type of investment is this for?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,87 +635,87 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>investment_performance_disclosure_consent_form</t>
+          <t>What is your phone number?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>description_2</t>
+          <t>investment_time</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>the_investment_performance_disclosure_consent_form</t>
+          <t>What time did you make this investment?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>form_description_2</t>
+          <t>experience</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>the_investment_performance_disclosure_consent_form</t>
+          <t>Which of the following options best describes your investment experience?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>form_category_2</t>
+          <t>consent_terms</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>investor_forms</t>
+          <t>Have you read and understood the terms and conditions?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,16 +727,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>form_title_2</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>investment_performance_disclosure_consent_form</t>
+          <t>Do you consent to the use of your contact information for follow-up and communication?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>comment_2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Do you have any further comments or questions?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -757,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -781,102 +804,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>investment_type_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>investment_forms</t>
+          <t>equity</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Investment Forms</t>
+          <t>Equity</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>investment_type_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>other_forms</t>
+          <t>fixed_income</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Other Forms</t>
+          <t>Fixed Income</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>investment_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>investor_forms</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Investor Forms</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>experience_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>other_forms</t>
+          <t>investment_beginner</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Other Forms</t>
+          <t>Investment Beginner</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>form_category_2_choices</t>
+          <t>experience_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>investor_forms</t>
+          <t>experienced_investor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Investor Forms</t>
+          <t>Experienced Investor</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>form_category_2_choices</t>
+          <t>experience_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>other_forms</t>
+          <t>investment_professional</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Other Forms</t>
+          <t>Investment Professional</t>
         </is>
       </c>
     </row>
